--- a/Information/Budgeting.xlsx
+++ b/Information/Budgeting.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofcambridgecloud-my.sharepoint.com/personal/je475_cam_ac_uk/Documents/Lab work/3GM2 - Technology for the Poorest Billion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{ED6ABE92-D3BC-4AB8-B3FF-790CDB917A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B97F8C3A-B055-4DCB-9BE6-D226F0F87C0E}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{ED6ABE92-D3BC-4AB8-B3FF-790CDB917A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34AFCB12-8ECE-4256-B3F8-7046DF025A44}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{3032395E-424D-4788-B377-478866993A03}"/>
   </bookViews>
@@ -92,9 +92,6 @@
     <t>The Pi Hut</t>
   </si>
   <si>
-    <t>DHT11 Temperature-Humidity Sensor - The Pi Hut</t>
-  </si>
-  <si>
     <t>Temperature Sensors</t>
   </si>
   <si>
@@ -144,6 +141,9 @@
   </si>
   <si>
     <t>https://www.amazon.co.uk/Kair-Plastic-Ducting-Pipe-100mm/dp/B00YLIOWXI/ref=sr_1_2_sspa?crid=279INPZQKQF91&amp;dib=eyJ2IjoiMSJ9.cCd9wZjcKZSJ81PhcjCCPX-uNYWbpBcvyVRN9O8QU9hmJ_SYZ69QPnH0uEovOiO9U_tMVo4m6iElDzLMbFS1OcfiVfZAYovKxA47m1phFHJfbeA7RbrHtz9dyd4OKdJkeq1Bjuf8m3xzMqIwI1_K6Lgm5GFdrYJ4lJXMNeo7WWfW6RhIUlPTguiQyiaL5mjjRh9RAFwK8vcoCcpKQKhX_aCIj1uR894pMuGozpueWG4FK286bKvKfkgk8ieuVZqR7LYomtGJq8ZSz6llLP_THf41q_hDwv4sCJKlvJecnw0._ougEZZqB_DtiMLKcXj8DGm9CumELT7UWA4K_5P-VUM&amp;dib_tag=se&amp;keywords=100mm%2Bdiameter%2Bpvc&amp;qid=1779809437&amp;sprefix=100mm%2Bdiameter%2Bpvc%2Caps%2C98&amp;sr=8-2-spons&amp;aref=JJ930bj3IU&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>DFR0067 | DFRobot Gravity: DHT11 Temperature &amp; Humidity Sensor For Arduino, Arduino Compatible Kit | RS</t>
   </si>
 </sst>
 </file>
@@ -306,10 +306,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -703,22 +703,22 @@
       <c r="B5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="18">
         <v>44.92</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B6" s="7"/>
-      <c r="C6" s="19"/>
+      <c r="C6" s="18"/>
       <c r="D6" s="17"/>
       <c r="E6" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
@@ -726,10 +726,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B7" s="7"/>
-      <c r="C7" s="19"/>
+      <c r="C7" s="18"/>
       <c r="D7" s="17"/>
       <c r="E7" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
@@ -737,10 +737,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B8" s="7"/>
-      <c r="C8" s="19"/>
+      <c r="C8" s="18"/>
       <c r="D8" s="17"/>
       <c r="E8" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
@@ -779,41 +779,41 @@
         <v>15</v>
       </c>
       <c r="C11" s="16">
-        <f>2*3.9</f>
-        <v>7.8</v>
+        <f>2*7.12</f>
+        <v>14.24</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="18" t="s">
-        <v>17</v>
+      <c r="E11" s="19" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B12" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
+      <c r="E12" s="19"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B13" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="8">
         <v>13.31</v>
       </c>
       <c r="D13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>20</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B14" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="13">
         <v>7.19</v>
@@ -822,62 +822,62 @@
         <v>5</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B15" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" s="15">
         <f>SUM(C3:C13)</f>
-        <v>127.53999999999999</v>
+        <v>133.97999999999999</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="E11:E12"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
     <mergeCell ref="C5:C8"/>
     <mergeCell ref="D5:D8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" display="https://www.amazon.co.uk/Marine-Blower-Electric-Ventilation-Caravan/dp/B0CT5LW2J1" xr:uid="{D3AEB23F-C33D-4949-8A4E-8C09F4EFC3B0}"/>
-    <hyperlink ref="E11" r:id="rId2" display="https://thepihut.com/products/dht11-temperature-humidity-sensor" xr:uid="{97FD9648-49A1-48C1-BC7A-71EB5F33F0F5}"/>
-    <hyperlink ref="E13" r:id="rId3" display="https://uk.rs-online.com/web/p/arduino/1927590" xr:uid="{20D9A4A5-4B10-42BD-A677-50DB16AB71F2}"/>
-    <hyperlink ref="E9" r:id="rId4" display="https://www.amazon.co.uk/Element-AC-Thermostatic-Aluminum-Constant-Temperature/dp/B07Y5DKHBH?th=1" xr:uid="{29AD6C15-E6A8-466F-A71B-EC60316FD0B1}"/>
-    <hyperlink ref="E14" r:id="rId5" display="https://www.amazon.co.uk/JZK-BTS7960B-Double-Stepper-H-Bridge/dp/B09HGBM5D2" xr:uid="{A8CE91F6-21B6-4EFF-AF34-6054ABF3441D}"/>
+    <hyperlink ref="E13" r:id="rId2" display="https://uk.rs-online.com/web/p/arduino/1927590" xr:uid="{20D9A4A5-4B10-42BD-A677-50DB16AB71F2}"/>
+    <hyperlink ref="E9" r:id="rId3" display="https://www.amazon.co.uk/Element-AC-Thermostatic-Aluminum-Constant-Temperature/dp/B07Y5DKHBH?th=1" xr:uid="{29AD6C15-E6A8-466F-A71B-EC60316FD0B1}"/>
+    <hyperlink ref="E14" r:id="rId4" display="https://www.amazon.co.uk/JZK-BTS7960B-Double-Stepper-H-Bridge/dp/B09HGBM5D2" xr:uid="{A8CE91F6-21B6-4EFF-AF34-6054ABF3441D}"/>
+    <hyperlink ref="E11" r:id="rId5" display="https://uk.rs-online.com/web/p/arduino-compatible-boards-kits/2163753?cm_mmc=UK-PLA-DS3A-_-google-_-CSS_UK_EN_PMAX_Catch+All-_--_-2163753&amp;matchtype=&amp;&amp;gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20567417192&amp;gbraid=0AAAAADkeWNPBw2HJdbGSP8F5CHG3OnAxN&amp;gclid=CjwKCAjwrNrQBhBjEiwAoR4VO8Bs9SOyBXVKtq_twSjvQzVa5AtAmWyxczlsRe95jQtBYem2SGTG6xoCl-IQAvD_BwE" xr:uid="{225427A8-82CF-49B6-868D-4EA3C54AF43C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
